--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:53</t>
+    <t xml:space="preserve">2026-09-09 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
@@ -57,6 +57,9 @@
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Combarbalá</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:42</t>
+    <t xml:space="preserve">2026-09-18 10:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -653,13 +653,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4302</v>
+        <v>4105</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>31.34</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31.2</v>
+        <v>31.34</v>
       </c>
     </row>
     <row r="12">
@@ -687,13 +687,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4305</v>
+        <v>4304</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>29.7</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="13">
@@ -704,13 +704,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4202</v>
+        <v>4305</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>27.99</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="14">
@@ -721,13 +721,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4203</v>
+        <v>4202</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>27.29</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4104</v>
+        <v>4203</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>26.79</v>
+        <v>27.29</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4104</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>26.79</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:05</t>
+    <t xml:space="preserve">2026-09-23 12:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:10</t>
+    <t xml:space="preserve">2026-10-02 13:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:36</t>
+    <t xml:space="preserve">2026-10-04 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:28</t>
+    <t xml:space="preserve">2026-10-05 09:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
